--- a/results/Int All Data -0.9/Rando_7_permute.xlsx
+++ b/results/Int All Data -0.9/Rando_7_permute.xlsx
@@ -440,117 +440,117 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8950031659261084</v>
+        <v>0.8945764369830698</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9149108014135348</v>
+        <v>0.8691377075221141</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9147049372657136</v>
+        <v>0.8720211872301857</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9124540506485017</v>
+        <v>0.8733749956577073</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9124540506485017</v>
+        <v>0.8725801587226396</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.913233886936173</v>
+        <v>0.8777445263427158</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.91230680745169</v>
+        <v>0.8838945943982845</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.909687812842449</v>
+        <v>0.8864249667617234</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9096291918914395</v>
+        <v>0.8822913015193288</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9018308290147259</v>
+        <v>0.8925464151610754</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9069801959874058</v>
+        <v>0.8915607147255828</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9073333033320385</v>
+        <v>0.8887358559685208</v>
       </c>
     </row>
     <row r="14">
@@ -560,1313 +560,1313 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9036849879836919</v>
+        <v>0.8848816764723531</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.903405502237465</v>
+        <v>0.8901769050032686</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9029787732944264</v>
+        <v>0.8887058546737281</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8998608097823169</v>
+        <v>0.8887058546737281</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8829688965523775</v>
+        <v>0.903889470492937</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8711391096878918</v>
+        <v>0.9047279277316178</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8668732018960819</v>
+        <v>0.9065670860531876</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8675794165853474</v>
+        <v>0.9055963862650915</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8592070815687836</v>
+        <v>0.8923541700220747</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.858500866879518</v>
+        <v>0.8797759298032863</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8711391096878918</v>
+        <v>0.8802762803447307</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8703892746950133</v>
+        <v>0.8726265423034048</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8581177582400925</v>
+        <v>0.8713613561216853</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8584708655847253</v>
+        <v>0.8685214967172268</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8608839960461452</v>
+        <v>0.8647559394668611</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8506425014132188</v>
+        <v>0.8647995597704743</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8506425014132188</v>
+        <v>0.8687409798738682</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8468319422206643</v>
+        <v>0.8683878725292354</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.844286569209829</v>
+        <v>0.864018341844227</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8461543471876154</v>
+        <v>0.8631798846055462</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8465074545322482</v>
+        <v>0.8631798846055462</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8528920063918548</v>
+        <v>0.8628731608416784</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.857246536429467</v>
+        <v>0.8554279053095976</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8590706941036403</v>
+        <v>0.8582963843702729</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8596146649486978</v>
+        <v>0.858986216773566</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8484774737646572</v>
+        <v>0.8601041597584738</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8477712590753916</v>
+        <v>0.8579268947396677</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8466819357467006</v>
+        <v>0.8519254515194866</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8440193208338465</v>
+        <v>0.8575165480826015</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8439606998828371</v>
+        <v>0.8573543042383935</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.842827756250533</v>
+        <v>0.843964844798565</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8186992149134857</v>
+        <v>0.8404773916558504</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8197585369473841</v>
+        <v>0.8384323691864597</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8171831626417561</v>
+        <v>0.8385768491061194</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8012047098874793</v>
+        <v>0.8130617347696059</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.806427698458565</v>
+        <v>0.757329395268638</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8132389792612102</v>
+        <v>0.7284032126649677</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.800468493903421</v>
+        <v>0.7175605078745504</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.788668708333728</v>
+        <v>0.7136463257887972</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7872712796025934</v>
+        <v>0.6977864965751153</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7818288078748662</v>
+        <v>0.6977864965751153</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7818288078748662</v>
+        <v>0.6789395647601633</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7550212693389925</v>
+        <v>0.6816908019188197</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7601706363116724</v>
+        <v>0.67139206797346</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7285546007775072</v>
+        <v>0.674218308369098</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7448983982466612</v>
+        <v>0.6595350430913334</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7093667989881669</v>
+        <v>0.6738652010244652</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7116926888423606</v>
+        <v>0.6738652010244652</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7025855194803143</v>
+        <v>0.674218308369098</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7029386268249471</v>
+        <v>0.6875191455631243</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7042038130066666</v>
+        <v>0.6834891032139282</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7030858700217588</v>
+        <v>0.6806792451042624</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6987613412789394</v>
+        <v>0.663023877872624</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7325560234704867</v>
+        <v>0.65400533075638</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7297747850170375</v>
+        <v>0.65400533075638</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7293044357703858</v>
+        <v>0.65400533075638</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7206676156549914</v>
+        <v>0.6798994088165911</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7274802780962126</v>
+        <v>0.6756621206809978</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7274802780962126</v>
+        <v>0.6660696014249036</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7255824988236335</v>
+        <v>0.6806206241532529</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6884898453512204</v>
+        <v>0.6032737333927043</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6851060151017043</v>
+        <v>0.6070542912904662</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6571082936210931</v>
+        <v>0.6050242694684718</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6609774737646572</v>
+        <v>0.6400555181855216</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6643163020719841</v>
+        <v>0.6431298613940181</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6405994890305793</v>
+        <v>0.6329483693506772</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6235767148898005</v>
+        <v>0.6316831831689578</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6195616731880007</v>
+        <v>0.6309769684796922</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6156474911022476</v>
+        <v>0.6225173928559022</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.598992824953498</v>
+        <v>0.6050678897720849</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5939757005302334</v>
+        <v>0.6050678897720849</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5931958642425621</v>
+        <v>0.5900165165022911</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.552441276412982</v>
+        <v>0.6008892225875011</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.552441276412982</v>
+        <v>0.601080086087926</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5259582255655244</v>
+        <v>0.6036104584513647</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5216473158315253</v>
+        <v>0.615336622422652</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.522882500718452</v>
+        <v>0.6053609945271322</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.530371376554146</v>
+        <v>0.6053609945271322</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5399338945154475</v>
+        <v>0.599711277013008</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5386823273425485</v>
+        <v>0.604301672493234</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5223507672436389</v>
+        <v>0.600079385005037</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5167010497295147</v>
+        <v>0.6007855996943026</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5174208834276006</v>
+        <v>0.5852338758830644</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5129627304967899</v>
+        <v>0.5841745538491662</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5129627304967899</v>
+        <v>0.5743611697978545</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.51442016181751</v>
+        <v>0.5760953235876496</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5019141615585515</v>
+        <v>0.5765220525306882</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5018405399601457</v>
+        <v>0.5765220525306882</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5021936473047784</v>
+        <v>0.5758158378414227</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5105209803791532</v>
+        <v>0.5741825436676741</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5102414946329262</v>
+        <v>0.5681060972105112</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5093880367468491</v>
+        <v>0.5642219164195508</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5033115902896862</v>
+        <v>0.5616765434087155</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.506444554449192</v>
+        <v>0.5542762898188238</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.506444554449192</v>
+        <v>0.5542762898188238</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.507856983827723</v>
+        <v>0.5546307788020325</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5007062146892656</v>
+        <v>0.5336638212807079</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5024717514124294</v>
+        <v>0.530485855179013</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5024717514124294</v>
+        <v>0.5208047136771166</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5021922656662025</v>
+        <v>0.5211578210217493</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5018391583215697</v>
+        <v>0.5306030970810319</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5004267289430386</v>
+        <v>0.5371212731286298</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5004267289430386</v>
+        <v>0.5330898491408577</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5256009733051638</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5214523074153726</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5217167925142032</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5222021424082512</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5</v>
+        <v>0.5072093900894671</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5</v>
+        <v>0.5060764464571629</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5</v>
+        <v>0.5078419831803267</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5078419831803267</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5078419831803267</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5085481978695923</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5025453730108352</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5025453730108352</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5025453730108352</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5021922656662025</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5</v>
+        <v>0.5014860509769369</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5</v>
+        <v>0.5011329436323041</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5</v>
+        <v>0.5011329436323041</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5</v>
+        <v>0.5004267289430386</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5004267289430386</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5004267289430386</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4997941358521789</v>
+        <v>0.5004267289430386</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4981172213748172</v>
+        <v>0.5000736215984058</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4991615427613192</v>
+        <v>0.5000736215984058</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4988820570150923</v>
+        <v>0.5004267289430386</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4980435997764114</v>
+        <v>0.4997941358521789</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4963666852990498</v>
+        <v>0.4997205142537731</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4960871995528228</v>
+        <v>0.4997205142537731</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4991615427613192</v>
+        <v>0.4997205142537731</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -1876,77 +1876,77 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4986025712688653</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4977641140301844</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4977641140301844</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4974846282839575</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4988820570150923</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1956,7 +1956,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B156" t="n">
